--- a/outputs/daily/hr_rankings_2026-10-17_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-17_full.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -811,7 +811,7 @@
         <v>39.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1068,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1095,7 +1091,7 @@
         <v>39.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1105,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1863,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -1893,17 +1885,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1912,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>48.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1930,22 +1922,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>39.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1959,7 +1951,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1997,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2027,97 +2019,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2143,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2173,17 +2165,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2192,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.1</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2206,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>39.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2281,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2296,12 +2284,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2311,97 +2299,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2427,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2457,7 +2445,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2476,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2490,11 +2478,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
@@ -2503,49 +2491,45 @@
         <v>39.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2565,12 +2549,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2580,7 +2564,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2595,67 +2579,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3831,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3880,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3894,11 +3878,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>32</v>
@@ -3907,49 +3891,45 @@
         <v>39.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3969,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3999,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4115,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -4145,17 +4125,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4164,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4178,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>39.6</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4211,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4249,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4279,97 +4259,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4395,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4425,7 +4405,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4444,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33</v>
+        <v>34.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4458,26 +4438,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>39.6</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>38.3</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4491,7 +4471,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4529,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4559,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4675,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4705,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4724,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>34.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4738,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
@@ -4751,49 +4731,45 @@
         <v>39.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4813,22 +4789,22 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4843,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4959,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4989,7 +4965,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5008,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>34.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5022,11 +4998,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -5035,49 +5011,45 @@
         <v>39.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5097,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5112,7 +5084,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5127,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5243,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -5273,17 +5245,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5292,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.6</v>
+        <v>33</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5306,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>39.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5381,27 +5349,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5411,97 +5379,97 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -5576,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5590,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5603,7 +5571,7 @@
         <v>39.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5613,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6167,7 +6131,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6186,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6200,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6213,7 +6177,7 @@
         <v>39.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6223,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6470,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6484,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6497,7 +6457,7 @@
         <v>39.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6507,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7265,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -7295,17 +7251,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7314,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>48.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7332,22 +7288,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>39.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7361,7 +7317,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7399,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7429,97 +7385,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -7545,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -7575,17 +7531,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7594,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.1</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7608,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>39.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7683,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7698,12 +7650,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7713,97 +7665,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7829,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7859,7 +7811,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7878,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7892,11 +7844,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
@@ -7905,49 +7857,45 @@
         <v>39.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7967,12 +7915,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7982,7 +7930,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7997,67 +7945,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -9233,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9282,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9296,11 +9244,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>32</v>
@@ -9309,49 +9257,45 @@
         <v>39.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9371,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9401,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9517,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -9547,17 +9491,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9566,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9580,26 +9524,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>39.6</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9613,7 +9557,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9651,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9681,97 +9625,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -9797,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9827,7 +9771,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9846,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33</v>
+        <v>34.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9860,26 +9804,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>39.6</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>38.3</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9893,7 +9837,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9931,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9961,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -10077,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10107,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10126,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>34.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10140,11 +10084,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
@@ -10153,49 +10097,45 @@
         <v>39.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10215,22 +10155,22 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10245,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10361,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10391,7 +10331,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10410,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>34.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10424,11 +10364,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -10437,49 +10377,45 @@
         <v>39.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10499,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10514,7 +10450,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -10529,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10645,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -10675,17 +10611,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10694,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.6</v>
+        <v>33</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10708,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>39.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10783,27 +10715,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10813,97 +10745,97 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -10978,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10992,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11005,7 +10937,7 @@
         <v>39.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -11015,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
